--- a/中原進捗コスト表.xlsx
+++ b/中原進捗コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fko2347054\Desktop\GitHub\DiaryLifeOnlline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03751E7A-4D74-40BE-A4FD-C0CA80FCD828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE079EB-8E06-45F8-9816-983E823E3893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4005" yWindow="-14445" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1098,14 +1098,14 @@
       </c>
       <c r="F3">
         <f>SUMIF(C3:C302,"完了",B3:B302)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>85</v>
       </c>
       <c r="H3">
         <f>SUM(D3:D302)</f>
-        <v>9.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1124,14 +1124,14 @@
       </c>
       <c r="F4" s="7">
         <f ca="1">NETWORKDAYS(F5,F6)</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="10">
         <f ca="1" xml:space="preserve"> F3 / F4</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="F6" s="8">
         <f ca="1">TODAY()</f>
-        <v>45593</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="G9" s="7">
         <f ca="1">NETWORKDAYS(TODAY(),F9)</f>
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H9" s="10">
         <f ca="1">($F$2 - $F$3) / G9</f>
-        <v>1.9714285714285715</v>
+        <v>2.140625</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1246,11 +1246,11 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" ref="G10:G11" ca="1" si="0">NETWORKDAYS(TODAY(),F10)</f>
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H10" s="10">
         <f ca="1">($F$2 - $F$3) / G10</f>
-        <v>1.5333333333333334</v>
+        <v>1.6309523809523809</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H11" s="10">
         <f ca="1">($F$2 - $F$3) / G11</f>
-        <v>1.2321428571428572</v>
+        <v>1.2924528301886793</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1445,7 +1445,9 @@
       <c r="C25" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="12"/>
+      <c r="D25" s="12">
+        <v>4</v>
+      </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="12" t="s">
@@ -1581,9 +1583,11 @@
         <v>1</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" s="12"/>
+        <v>84</v>
+      </c>
+      <c r="D37" s="12">
+        <v>6</v>
+      </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="12" t="s">
@@ -2006,6 +2010,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100534661B278935E44B366872DF9464E45" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="87be336555b78707b8880fee16249c2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="56f67181-167d-4f85-a438-a55f61d398e9" xmlns:ns3="c2562f78-638f-4b8f-b708-acdd87129c74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b22ecc2f48af7f73de819eeebf1146e0" ns2:_="" ns3:_="">
     <xsd:import namespace="56f67181-167d-4f85-a438-a55f61d398e9"/>
@@ -2240,16 +2253,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C503E31-A055-4E3E-87D4-A7218666B93F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9235FD93-4680-4960-95C4-E56056A8E66E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2266,12 +2278,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C503E31-A055-4E3E-87D4-A7218666B93F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/中原進捗コスト表.xlsx
+++ b/中原進捗コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fko2347054\Desktop\GitHub\DiaryLifeOnlline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE079EB-8E06-45F8-9816-983E823E3893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274435F3-5C61-430B-8EC9-576C65338B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4005" yWindow="-14445" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="H3">
         <f>SUM(D3:D302)</f>
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1124,14 +1124,14 @@
       </c>
       <c r="F4" s="7">
         <f ca="1">NETWORKDAYS(F5,F6)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="10">
         <f ca="1" xml:space="preserve"> F3 / F4</f>
-        <v>1</v>
+        <v>0.91666666666666663</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="F6" s="8">
         <f ca="1">TODAY()</f>
-        <v>45601</v>
+        <v>45602</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="G9" s="7">
         <f ca="1">NETWORKDAYS(TODAY(),F9)</f>
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H9" s="10">
         <f ca="1">($F$2 - $F$3) / G9</f>
-        <v>2.140625</v>
+        <v>2.1746031746031744</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1246,11 +1246,11 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" ref="G10:G11" ca="1" si="0">NETWORKDAYS(TODAY(),F10)</f>
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H10" s="10">
         <f ca="1">($F$2 - $F$3) / G10</f>
-        <v>1.6309523809523809</v>
+        <v>1.6506024096385543</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H11" s="10">
         <f ca="1">($F$2 - $F$3) / G11</f>
-        <v>1.2924528301886793</v>
+        <v>1.3047619047619048</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1396,7 +1396,7 @@
         <v>84</v>
       </c>
       <c r="D21" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2010,15 +2010,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100534661B278935E44B366872DF9464E45" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="87be336555b78707b8880fee16249c2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="56f67181-167d-4f85-a438-a55f61d398e9" xmlns:ns3="c2562f78-638f-4b8f-b708-acdd87129c74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b22ecc2f48af7f73de819eeebf1146e0" ns2:_="" ns3:_="">
     <xsd:import namespace="56f67181-167d-4f85-a438-a55f61d398e9"/>
@@ -2253,15 +2244,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C503E31-A055-4E3E-87D4-A7218666B93F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9235FD93-4680-4960-95C4-E56056A8E66E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2278,4 +2270,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C503E31-A055-4E3E-87D4-A7218666B93F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/中原進捗コスト表.xlsx
+++ b/中原進捗コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fko2347054\Desktop\GitHub\DiaryLifeOnlline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274435F3-5C61-430B-8EC9-576C65338B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6019CFE9-9FCA-4A19-A553-C12D449029A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4005" yWindow="-14445" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="H3">
         <f>SUM(D3:D302)</f>
-        <v>20.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1124,14 +1124,14 @@
       </c>
       <c r="F4" s="7">
         <f ca="1">NETWORKDAYS(F5,F6)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="10">
         <f ca="1" xml:space="preserve"> F3 / F4</f>
-        <v>0.91666666666666663</v>
+        <v>0.84615384615384615</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="F6" s="8">
         <f ca="1">TODAY()</f>
-        <v>45602</v>
+        <v>45603</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1219,11 +1219,11 @@
       </c>
       <c r="G9" s="7">
         <f ca="1">NETWORKDAYS(TODAY(),F9)</f>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H9" s="10">
         <f ca="1">($F$2 - $F$3) / G9</f>
-        <v>2.1746031746031744</v>
+        <v>2.2096774193548385</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1246,11 +1246,11 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" ref="G10:G11" ca="1" si="0">NETWORKDAYS(TODAY(),F10)</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H10" s="10">
         <f ca="1">($F$2 - $F$3) / G10</f>
-        <v>1.6506024096385543</v>
+        <v>1.6707317073170731</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H11" s="10">
         <f ca="1">($F$2 - $F$3) / G11</f>
-        <v>1.3047619047619048</v>
+        <v>1.3173076923076923</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1396,7 +1396,7 @@
         <v>84</v>
       </c>
       <c r="D21" s="12">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1572,7 +1572,7 @@
         <v>84</v>
       </c>
       <c r="D36" s="12">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2010,6 +2010,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100534661B278935E44B366872DF9464E45" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="87be336555b78707b8880fee16249c2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="56f67181-167d-4f85-a438-a55f61d398e9" xmlns:ns3="c2562f78-638f-4b8f-b708-acdd87129c74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b22ecc2f48af7f73de819eeebf1146e0" ns2:_="" ns3:_="">
     <xsd:import namespace="56f67181-167d-4f85-a438-a55f61d398e9"/>
@@ -2244,16 +2253,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C503E31-A055-4E3E-87D4-A7218666B93F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9235FD93-4680-4960-95C4-E56056A8E66E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2270,12 +2278,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C503E31-A055-4E3E-87D4-A7218666B93F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/中原進捗コスト表.xlsx
+++ b/中原進捗コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fko2347054\Desktop\GitHub\DiaryLifeOnlline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6019CFE9-9FCA-4A19-A553-C12D449029A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5077687C-D987-4C78-81BF-08DBEFD95848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4005" yWindow="-14445" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="87">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -581,6 +581,16 @@
     <t>実コスト</t>
     <rPh sb="0" eb="1">
       <t>ジツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実コスト/日数</t>
+    <rPh sb="0" eb="1">
+      <t>ジツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニッスウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -739,7 +749,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -761,6 +771,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1041,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
@@ -1052,16 +1063,17 @@
     <col min="6" max="6" width="14.375" customWidth="1"/>
     <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
@@ -1082,7 +1094,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" s="16" t="s">
         <v>5</v>
       </c>
@@ -1098,17 +1110,17 @@
       </c>
       <c r="F3">
         <f>SUMIF(C3:C302,"完了",B3:B302)</f>
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>85</v>
       </c>
       <c r="H3">
         <f>SUM(D3:D302)</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="16" t="s">
         <v>8</v>
       </c>
@@ -1124,17 +1136,24 @@
       </c>
       <c r="F4" s="7">
         <f ca="1">NETWORKDAYS(F5,F6)</f>
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="21" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="10">
         <f ca="1" xml:space="preserve"> F3 / F4</f>
-        <v>0.84615384615384615</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>1.6111111111111112</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4">
+        <f ca="1">H3/F4</f>
+        <v>2.1111111111111112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="17" t="s">
         <v>11</v>
       </c>
@@ -1149,7 +1168,7 @@
         <v>45587</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:10">
       <c r="A6" s="12" t="s">
         <v>13</v>
       </c>
@@ -1167,10 +1186,10 @@
       </c>
       <c r="F6" s="8">
         <f ca="1">TODAY()</f>
-        <v>45603</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>45610</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="12" t="s">
         <v>15</v>
       </c>
@@ -1182,7 +1201,7 @@
       </c>
       <c r="D7" s="12"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:10">
       <c r="A8" s="12" t="s">
         <v>16</v>
       </c>
@@ -1200,7 +1219,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:10">
       <c r="A9" s="12" t="s">
         <v>19</v>
       </c>
@@ -1219,14 +1238,14 @@
       </c>
       <c r="G9" s="7">
         <f ca="1">NETWORKDAYS(TODAY(),F9)</f>
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H9" s="10">
         <f ca="1">($F$2 - $F$3) / G9</f>
-        <v>2.2096774193548385</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>2.0877192982456139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="12" t="s">
         <v>21</v>
       </c>
@@ -1246,14 +1265,14 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" ref="G10:G11" ca="1" si="0">NETWORKDAYS(TODAY(),F10)</f>
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H10" s="10">
         <f ca="1">($F$2 - $F$3) / G10</f>
-        <v>1.6707317073170731</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>1.5454545454545454</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="12" t="s">
         <v>23</v>
       </c>
@@ -1261,9 +1280,11 @@
         <v>2</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="12"/>
+        <v>84</v>
+      </c>
+      <c r="D11" s="12">
+        <v>2</v>
+      </c>
       <c r="E11" s="4" t="s">
         <v>24</v>
       </c>
@@ -1272,14 +1293,14 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H11" s="10">
         <f ca="1">($F$2 - $F$3) / G11</f>
-        <v>1.3173076923076923</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>1.202020202020202</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="12" t="s">
         <v>25</v>
       </c>
@@ -1291,7 +1312,7 @@
       </c>
       <c r="D12" s="12"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:10">
       <c r="A13" s="17" t="s">
         <v>26</v>
       </c>
@@ -1299,7 +1320,7 @@
       <c r="C13" s="17"/>
       <c r="D13" s="12"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:10">
       <c r="A14" s="12" t="s">
         <v>27</v>
       </c>
@@ -1311,7 +1332,7 @@
       </c>
       <c r="D14" s="12"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:10">
       <c r="A15" s="12" t="s">
         <v>28</v>
       </c>
@@ -1325,7 +1346,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:10">
       <c r="A16" s="12" t="s">
         <v>29</v>
       </c>
@@ -1443,7 +1464,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="D25" s="12">
         <v>4</v>
@@ -1631,9 +1652,11 @@
         <v>8</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="12"/>
+        <v>84</v>
+      </c>
+      <c r="D41" s="12">
+        <v>8</v>
+      </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="12" t="s">
@@ -1655,9 +1678,11 @@
         <v>4</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="12"/>
+        <v>84</v>
+      </c>
+      <c r="D43" s="12">
+        <v>4</v>
+      </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="17" t="s">
@@ -2010,15 +2035,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100534661B278935E44B366872DF9464E45" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="87be336555b78707b8880fee16249c2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="56f67181-167d-4f85-a438-a55f61d398e9" xmlns:ns3="c2562f78-638f-4b8f-b708-acdd87129c74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b22ecc2f48af7f73de819eeebf1146e0" ns2:_="" ns3:_="">
     <xsd:import namespace="56f67181-167d-4f85-a438-a55f61d398e9"/>
@@ -2253,15 +2269,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C503E31-A055-4E3E-87D4-A7218666B93F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9235FD93-4680-4960-95C4-E56056A8E66E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2278,4 +2295,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C503E31-A055-4E3E-87D4-A7218666B93F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/中原進捗コスト表.xlsx
+++ b/中原進捗コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fko2347054\Desktop\GitHub\DiaryLifeOnlline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5077687C-D987-4C78-81BF-08DBEFD95848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB215CC-F46B-4EFD-964C-4E44F8ABC4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4005" yWindow="-14445" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1110,14 +1110,14 @@
       </c>
       <c r="F3">
         <f>SUMIF(C3:C302,"完了",B3:B302)</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>85</v>
       </c>
       <c r="H3">
         <f>SUM(D3:D302)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1136,21 +1136,21 @@
       </c>
       <c r="F4" s="7">
         <f ca="1">NETWORKDAYS(F5,F6)</f>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G4" s="21" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="10">
         <f ca="1" xml:space="preserve"> F3 / F4</f>
-        <v>1.6111111111111112</v>
+        <v>1.3478260869565217</v>
       </c>
       <c r="I4" s="21" t="s">
         <v>86</v>
       </c>
       <c r="J4">
         <f ca="1">H3/F4</f>
-        <v>2.1111111111111112</v>
+        <v>1.7391304347826086</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="F6" s="8">
         <f ca="1">TODAY()</f>
-        <v>45610</v>
+        <v>45617</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1238,11 +1238,11 @@
       </c>
       <c r="G9" s="7">
         <f ca="1">NETWORKDAYS(TODAY(),F9)</f>
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H9" s="10">
         <f ca="1">($F$2 - $F$3) / G9</f>
-        <v>2.0877192982456139</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1265,11 +1265,11 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" ref="G10:G11" ca="1" si="0">NETWORKDAYS(TODAY(),F10)</f>
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H10" s="10">
         <f ca="1">($F$2 - $F$3) / G10</f>
-        <v>1.5454545454545454</v>
+        <v>1.625</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1293,11 +1293,11 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H11" s="10">
         <f ca="1">($F$2 - $F$3) / G11</f>
-        <v>1.202020202020202</v>
+        <v>1.2446808510638299</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1522,9 +1522,11 @@
         <v>2</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="12"/>
+        <v>84</v>
+      </c>
+      <c r="D30" s="12">
+        <v>2</v>
+      </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="12" t="s">
@@ -2035,6 +2037,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100534661B278935E44B366872DF9464E45" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="87be336555b78707b8880fee16249c2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="56f67181-167d-4f85-a438-a55f61d398e9" xmlns:ns3="c2562f78-638f-4b8f-b708-acdd87129c74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b22ecc2f48af7f73de819eeebf1146e0" ns2:_="" ns3:_="">
     <xsd:import namespace="56f67181-167d-4f85-a438-a55f61d398e9"/>
@@ -2269,16 +2280,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C503E31-A055-4E3E-87D4-A7218666B93F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9235FD93-4680-4960-95C4-E56056A8E66E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2295,12 +2305,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C503E31-A055-4E3E-87D4-A7218666B93F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/中原進捗コスト表.xlsx
+++ b/中原進捗コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fko2347054\Desktop\GitHub\DiaryLifeOnlline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB215CC-F46B-4EFD-964C-4E44F8ABC4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE52B68-8D68-4BCC-A45B-5F1E539EA203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4005" yWindow="-14445" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="84">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -63,13 +63,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・クラス設計</t>
-    <rPh sb="4" eb="6">
-      <t>セッケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>未完</t>
     <rPh sb="0" eb="2">
       <t>ミカン</t>
@@ -84,13 +77,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・ライブラリ設計</t>
-    <rPh sb="6" eb="8">
-      <t>セッケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>現在の日数(土日除く)</t>
     <rPh sb="0" eb="2">
       <t>ゲンザイ</t>
@@ -247,16 +233,6 @@
       <t>ア</t>
     </rPh>
     <rPh sb="12" eb="14">
-      <t>ハンテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　アイテムの当たり判定</t>
-    <rPh sb="8" eb="9">
-      <t>ア</t>
-    </rPh>
-    <rPh sb="11" eb="13">
       <t>ハンテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -698,13 +674,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -766,12 +742,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1058,7 +1034,7 @@
     <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="2" width="12.375" customWidth="1"/>
     <col min="3" max="3" width="12.625" customWidth="1"/>
-    <col min="4" max="4" width="8.875" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.375" customWidth="1"/>
     <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
@@ -1083,85 +1059,87 @@
       <c r="C2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="20" t="s">
-        <v>85</v>
+      <c r="D2" s="19" t="s">
+        <v>82</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F2">
         <f>SUM(B3:B302)</f>
-        <v>148</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="12">
+        <v>9</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="5" t="s">
-        <v>7</v>
       </c>
       <c r="F3">
         <f>SUMIF(C3:C302,"完了",B3:B302)</f>
-        <v>31</v>
+        <v>33.5</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H3">
         <f>SUM(D3:D302)</f>
-        <v>40</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="12">
-        <v>4</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="12"/>
+      <c r="A4" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="21">
+        <v>2</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="21">
+        <v>3</v>
+      </c>
       <c r="E4" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" s="7">
         <f ca="1">NETWORKDAYS(F5,F6)</f>
-        <v>23</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>10</v>
+        <v>25</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>8</v>
       </c>
       <c r="H4" s="10">
         <f ca="1" xml:space="preserve"> F3 / F4</f>
-        <v>1.3478260869565217</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>86</v>
+        <v>1.34</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>83</v>
       </c>
       <c r="J4">
         <f ca="1">H3/F4</f>
-        <v>1.7391304347826086</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="12">
+        <v>6</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>5</v>
+      </c>
       <c r="D5" s="12"/>
       <c r="E5" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" s="8">
         <f>DATE(2024,10,22)</f>
@@ -1170,94 +1148,94 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" s="12">
-        <v>3</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D6" s="12"/>
       <c r="E6" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F6" s="8">
         <f ca="1">TODAY()</f>
-        <v>45617</v>
+        <v>45621</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="12"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B8" s="12">
         <v>1</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="12"/>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="21">
+        <v>2</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="21">
+        <v>2</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="12">
-        <v>1</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="F9" s="1">
         <v>45689</v>
       </c>
       <c r="G9" s="7">
         <f ca="1">NETWORKDAYS(TODAY(),F9)</f>
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H9" s="10">
         <f ca="1">($F$2 - $F$3) / G9</f>
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1">
         <f>DATE(2025,3,1)</f>
@@ -1265,130 +1243,136 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" ref="G10:G11" ca="1" si="0">NETWORKDAYS(TODAY(),F10)</f>
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H10" s="10">
         <f ca="1">($F$2 - $F$3) / G10</f>
-        <v>1.625</v>
+        <v>1.4857142857142858</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="12">
-        <v>2</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="12">
-        <v>2</v>
-      </c>
+      <c r="A11" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
       <c r="E11" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1">
         <v>45748</v>
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H11" s="10">
         <f ca="1">($F$2 - $F$3) / G11</f>
-        <v>1.2446808510638299</v>
+        <v>1.1304347826086956</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="12">
-        <v>3</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="21">
+        <v>2</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="21">
+        <v>1</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="21">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="21">
+        <v>4</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="21">
         <v>6</v>
       </c>
-      <c r="D12" s="12"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="12"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="12"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="12"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="12"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="12"/>
     </row>
@@ -1400,11 +1384,9 @@
         <v>1</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" s="12">
-        <v>1.5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D20" s="12"/>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="12" t="s">
@@ -1414,33 +1396,33 @@
         <v>4</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="12">
-        <v>6</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D21" s="12"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="12">
-        <v>1</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="12"/>
+      <c r="B22" s="21">
+        <v>4</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="21">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="12" t="s">
         <v>36</v>
       </c>
       <c r="B23" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" s="12"/>
     </row>
@@ -1449,10 +1431,10 @@
         <v>37</v>
       </c>
       <c r="B24" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" s="12"/>
     </row>
@@ -1461,128 +1443,132 @@
         <v>38</v>
       </c>
       <c r="B25" s="12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="12">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D25" s="12"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="12">
-        <v>4</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="12"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="21">
         <v>2</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="12"/>
+      <c r="C27" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="21">
+        <v>2</v>
+      </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="12" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B28" s="12">
         <v>1</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" s="12"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="A29" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="12">
+        <v>4</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>5</v>
+      </c>
       <c r="D29" s="12"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" s="12">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D30" s="12"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="12" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B31" s="12">
+        <v>2</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="12"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="21">
         <v>1</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C33" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="21">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="21">
+        <v>1</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" s="21">
         <v>6</v>
       </c>
-      <c r="D31" s="12"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="12">
-        <v>4</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="12"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="12">
-        <v>6</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="12"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="12">
-        <v>2</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="12"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="12"/>
+      <c r="B35" s="21">
+        <v>1</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="12" t="s">
@@ -1592,38 +1578,30 @@
         <v>1</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" s="12">
-        <v>1.5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D36" s="12"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="12">
-        <v>1</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" s="12">
-        <v>6</v>
-      </c>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B38" s="12">
-        <v>1</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D38" s="12">
-        <v>1</v>
+      <c r="B38" s="21">
+        <v>8</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="21">
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1631,44 +1609,44 @@
         <v>51</v>
       </c>
       <c r="B39" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39" s="12"/>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="12"/>
+      <c r="B40" s="21">
+        <v>4</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="21">
+        <v>4</v>
+      </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B41" s="12">
-        <v>8</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" s="12">
-        <v>8</v>
-      </c>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="12" t="s">
         <v>54</v>
       </c>
       <c r="B42" s="12">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D42" s="12"/>
     </row>
@@ -1677,44 +1655,42 @@
         <v>55</v>
       </c>
       <c r="B43" s="12">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D43" s="12">
-        <v>4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D43" s="12"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
+      <c r="B44" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>5</v>
+      </c>
       <c r="D44" s="12"/>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B45" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="12"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="12" t="s">
         <v>58</v>
       </c>
       <c r="B46" s="12">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46" s="12"/>
     </row>
@@ -1723,19 +1699,23 @@
         <v>59</v>
       </c>
       <c r="B47" s="12">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47" s="12"/>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
+      <c r="B48" s="12">
+        <v>2</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>5</v>
+      </c>
       <c r="D48" s="12"/>
     </row>
     <row r="49" spans="1:4">
@@ -1746,31 +1726,27 @@
         <v>2</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49" s="12"/>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B50" s="12">
-        <v>2</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D50" s="12"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="12" t="s">
         <v>63</v>
       </c>
       <c r="B51" s="12">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51" s="12"/>
     </row>
@@ -1779,30 +1755,30 @@
         <v>64</v>
       </c>
       <c r="B52" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52" s="12"/>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="12"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="12" t="s">
         <v>66</v>
       </c>
       <c r="B54" s="12">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D54" s="12"/>
     </row>
@@ -1811,42 +1787,42 @@
         <v>67</v>
       </c>
       <c r="B55" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55" s="12"/>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
+      <c r="B56" s="12">
+        <v>2</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>5</v>
+      </c>
       <c r="D56" s="12"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B57" s="12">
-        <v>2</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="12"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="12" t="s">
         <v>70</v>
       </c>
       <c r="B58" s="12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58" s="12"/>
     </row>
@@ -1855,19 +1831,23 @@
         <v>71</v>
       </c>
       <c r="B59" s="12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C59" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="12"/>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" s="12">
         <v>6</v>
       </c>
-      <c r="D59" s="12"/>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
+      <c r="C60" s="12" t="s">
+        <v>5</v>
+      </c>
       <c r="D60" s="12"/>
     </row>
     <row r="61" spans="1:4">
@@ -1875,34 +1855,30 @@
         <v>73</v>
       </c>
       <c r="B61" s="12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D61" s="12"/>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B62" s="12">
-        <v>6</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D62" s="12"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B63" s="12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D63" s="12"/>
     </row>
@@ -1911,19 +1887,23 @@
         <v>76</v>
       </c>
       <c r="B64" s="12">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D64" s="12"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="18" t="s">
+      <c r="A65" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
+      <c r="B65" s="12">
+        <v>2</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>5</v>
+      </c>
       <c r="D65" s="12"/>
     </row>
     <row r="66" spans="1:6">
@@ -1934,73 +1914,39 @@
         <v>2</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D66" s="12"/>
       <c r="F66" s="1"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="12" t="s">
+      <c r="A67" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B67" s="12">
+      <c r="B67" s="18">
         <v>1</v>
       </c>
-      <c r="C67" s="12" t="s">
-        <v>6</v>
+      <c r="C67" s="18" t="s">
+        <v>5</v>
       </c>
       <c r="D67" s="12"/>
       <c r="F67" s="1"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="17" t="s">
         <v>80</v>
       </c>
       <c r="B68" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D68" s="12"/>
       <c r="F68" s="1"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B69" s="12">
-        <v>2</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D69" s="12"/>
       <c r="F69" s="1"/>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="B70" s="19">
-        <v>1</v>
-      </c>
-      <c r="C70" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D70" s="12"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B71" s="12">
-        <v>3</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D71" s="12"/>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="11"/>

--- a/中原進捗コスト表.xlsx
+++ b/中原進捗コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fko2347054\Desktop\GitHub\DiaryLifeOnlline\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fko2347054\Desktop\GitHub\DiaryLifeOnllin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE52B68-8D68-4BCC-A45B-5F1E539EA203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED3BF4A-ED28-4632-8436-D53414E954C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4005" yWindow="-14445" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4005" yWindow="-14445" windowWidth="21600" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アルファ" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="83">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -264,10 +264,6 @@
   </si>
   <si>
     <t>　―　移動</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　―　ダッシュ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -725,7 +721,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -748,6 +744,7 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1028,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
@@ -1060,14 +1057,14 @@
         <v>3</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F2">
-        <f>SUM(B3:B302)</f>
-        <v>137.5</v>
+        <f>SUM(B3:B301)</f>
+        <v>136.5</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1081,15 +1078,15 @@
         <v>6</v>
       </c>
       <c r="F3">
-        <f>SUMIF(C3:C302,"完了",B3:B302)</f>
-        <v>33.5</v>
+        <f>SUMIF(C3:C301,"完了",B3:B301)</f>
+        <v>34.5</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H3">
-        <f>SUM(D3:D302)</f>
-        <v>42.5</v>
+        <f>SUM(D3:D301)</f>
+        <v>102.5</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1100,7 +1097,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D4" s="21">
         <v>3</v>
@@ -1110,21 +1107,21 @@
       </c>
       <c r="F4" s="7">
         <f ca="1">NETWORKDAYS(F5,F6)</f>
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>8</v>
       </c>
       <c r="H4" s="10">
         <f ca="1" xml:space="preserve"> F3 / F4</f>
-        <v>1.34</v>
+        <v>0.84146341463414631</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J4">
         <f ca="1">H3/F4</f>
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1162,7 +1159,7 @@
       </c>
       <c r="F6" s="8">
         <f ca="1">TODAY()</f>
-        <v>45621</v>
+        <v>45643</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1203,7 +1200,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D9" s="21">
         <v>2</v>
@@ -1216,11 +1213,11 @@
       </c>
       <c r="G9" s="7">
         <f ca="1">NETWORKDAYS(TODAY(),F9)</f>
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="H9" s="10">
         <f ca="1">($F$2 - $F$3) / G9</f>
-        <v>2.08</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1243,11 +1240,11 @@
       </c>
       <c r="G10" s="7">
         <f t="shared" ref="G10:G11" ca="1" si="0">NETWORKDAYS(TODAY(),F10)</f>
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="H10" s="10">
         <f ca="1">($F$2 - $F$3) / G10</f>
-        <v>1.4857142857142858</v>
+        <v>1.8888888888888888</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1265,11 +1262,11 @@
       </c>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="H11" s="10">
         <f ca="1">($F$2 - $F$3) / G11</f>
-        <v>1.1304347826086956</v>
+        <v>1.3421052631578947</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1280,7 +1277,7 @@
         <v>0.5</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D12" s="21">
         <v>0.5</v>
@@ -1294,7 +1291,7 @@
         <v>0.5</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" s="21">
         <v>0.5</v>
@@ -1308,7 +1305,7 @@
         <v>0.5</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D14" s="21">
         <v>0.5</v>
@@ -1330,7 +1327,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D16" s="21">
         <v>2</v>
@@ -1344,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D17" s="21">
         <v>1.5</v>
@@ -1358,7 +1355,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D18" s="21">
         <v>6</v>
@@ -1381,7 +1378,7 @@
         <v>33</v>
       </c>
       <c r="B20" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>5</v>
@@ -1389,37 +1386,37 @@
       <c r="D20" s="12"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="21">
         <v>4</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="12"/>
+      <c r="C21" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="21">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="12">
         <v>4</v>
       </c>
-      <c r="C22" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="21">
-        <v>4</v>
-      </c>
+      <c r="C22" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="12"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="12" t="s">
         <v>36</v>
       </c>
       <c r="B23" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>5</v>
@@ -1431,53 +1428,53 @@
         <v>37</v>
       </c>
       <c r="B24" s="12">
+        <v>1</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="12"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="21">
         <v>2</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="12"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="12">
+      <c r="C26" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="12">
         <v>1</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="12"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="21">
-        <v>2</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" s="21">
-        <v>2</v>
-      </c>
+      <c r="C27" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="12"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="12" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B28" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>5</v>
@@ -1489,7 +1486,7 @@
         <v>41</v>
       </c>
       <c r="B29" s="12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>5</v>
@@ -1501,7 +1498,7 @@
         <v>42</v>
       </c>
       <c r="B30" s="12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>5</v>
@@ -1509,24 +1506,26 @@
       <c r="D30" s="12"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="12">
-        <v>2</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="12"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
+      <c r="B32" s="21">
+        <v>1</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="21">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="21" t="s">
@@ -1536,10 +1535,10 @@
         <v>1</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D33" s="21">
-        <v>1.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1550,93 +1549,93 @@
         <v>1</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D34" s="21">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="21">
+      <c r="B35" s="22">
         <v>1</v>
       </c>
-      <c r="C35" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" s="21">
-        <v>1</v>
+      <c r="C35" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="22">
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B36" s="12">
-        <v>1</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="12"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
+      <c r="B37" s="21">
+        <v>8</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" s="21">
+        <v>8</v>
+      </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B38" s="21">
-        <v>8</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D38" s="21">
-        <v>8</v>
-      </c>
+      <c r="B38" s="12">
+        <v>4</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="12"/>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="21">
         <v>4</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="12"/>
+      <c r="C39" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="21">
+        <v>4</v>
+      </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="21">
-        <v>4</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" s="21">
-        <v>4</v>
-      </c>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
+      <c r="B41" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="12"/>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="12" t="s">
@@ -1663,24 +1662,24 @@
       <c r="D43" s="12"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="12"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
+      <c r="B45" s="12">
+        <v>2</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="12"/>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="12" t="s">
@@ -1719,31 +1718,31 @@
       <c r="D48" s="12"/>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B49" s="12">
-        <v>2</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49" s="12"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
+      <c r="B50" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="12"/>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="12" t="s">
         <v>63</v>
       </c>
       <c r="B51" s="12">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>5</v>
@@ -1751,24 +1750,24 @@
       <c r="D51" s="12"/>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B52" s="12">
-        <v>4</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="12"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="B53" s="16"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
+      <c r="B53" s="12">
+        <v>2</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="12"/>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="12" t="s">
@@ -1795,24 +1794,24 @@
       <c r="D55" s="12"/>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B56" s="12">
-        <v>2</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56" s="12"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B57" s="16"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
+      <c r="B57" s="12">
+        <v>6</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="12"/>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="12" t="s">
@@ -1843,7 +1842,7 @@
         <v>72</v>
       </c>
       <c r="B60" s="12">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>5</v>
@@ -1851,31 +1850,31 @@
       <c r="D60" s="12"/>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B61" s="12">
-        <v>12</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="12"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
+      <c r="B62" s="12">
+        <v>2</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" s="12"/>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="12" t="s">
         <v>75</v>
       </c>
       <c r="B63" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>5</v>
@@ -1887,7 +1886,7 @@
         <v>76</v>
       </c>
       <c r="B64" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>5</v>
@@ -1905,55 +1904,43 @@
         <v>5</v>
       </c>
       <c r="D65" s="12"/>
+      <c r="F65" s="1"/>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B66" s="12">
-        <v>2</v>
-      </c>
-      <c r="C66" s="12" t="s">
+      <c r="B66" s="18">
+        <v>1</v>
+      </c>
+      <c r="C66" s="18" t="s">
         <v>5</v>
       </c>
       <c r="D66" s="12"/>
       <c r="F66" s="1"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="18" t="s">
+      <c r="A67" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B67" s="18">
-        <v>1</v>
-      </c>
-      <c r="C67" s="18" t="s">
+      <c r="B67" s="12">
+        <v>3</v>
+      </c>
+      <c r="C67" s="12" t="s">
         <v>5</v>
       </c>
       <c r="D67" s="12"/>
       <c r="F67" s="1"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="12">
-        <v>3</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68" s="12"/>
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="1:6">
-      <c r="F69" s="1"/>
+    <row r="75" spans="1:6">
+      <c r="A75" s="11"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="11"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1983,15 +1970,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100534661B278935E44B366872DF9464E45" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="87be336555b78707b8880fee16249c2c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="56f67181-167d-4f85-a438-a55f61d398e9" xmlns:ns3="c2562f78-638f-4b8f-b708-acdd87129c74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b22ecc2f48af7f73de819eeebf1146e0" ns2:_="" ns3:_="">
     <xsd:import namespace="56f67181-167d-4f85-a438-a55f61d398e9"/>
@@ -2226,15 +2204,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C503E31-A055-4E3E-87D4-A7218666B93F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9235FD93-4680-4960-95C4-E56056A8E66E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2251,4 +2230,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C503E31-A055-4E3E-87D4-A7218666B93F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>